--- a/artfynd/A 35037-2021 artfynd.xlsx
+++ b/artfynd/A 35037-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35037-2021 artfynd.xlsx
+++ b/artfynd/A 35037-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86869756</v>
+        <v>86869915</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>354272.157630272</v>
+        <v>354272</v>
       </c>
       <c r="R2" t="n">
-        <v>6336693.217933291</v>
+        <v>6336693</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,24 +747,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera stora bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,12 +780,7 @@
         <v>86870002</v>
       </c>
       <c r="B3" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>354272.157630272</v>
+        <v>354272</v>
       </c>
       <c r="R3" t="n">
-        <v>6336693.217933291</v>
+        <v>6336693</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +849,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86869915</v>
+        <v>86869756</v>
       </c>
       <c r="B4" t="n">
-        <v>93146</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2666</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>354272.157630272</v>
+        <v>354272</v>
       </c>
       <c r="R4" t="n">
-        <v>6336693.217933291</v>
+        <v>6336693</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,19 +956,14 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera stora bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
